--- a/DATA/BD_SUBNA.xlsx
+++ b/DATA/BD_SUBNA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebasteitor\Desktop\MODELOS ECONOMETRICOS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7FB114-103A-4562-93E5-BFA2F170361B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD55D335-8925-448D-BA10-AA582AAB68D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66D934FB-75C9-48D1-8F66-592025DC4A00}"/>
+    <workbookView xWindow="8685" yWindow="0" windowWidth="18495" windowHeight="15585" xr2:uid="{66D934FB-75C9-48D1-8F66-592025DC4A00}"/>
   </bookViews>
   <sheets>
     <sheet name="base_subna" sheetId="2" r:id="rId1"/>
